--- a/exports/historial_compras/historial_compras_hasta_2026-07-07.xlsx
+++ b/exports/historial_compras/historial_compras_hasta_2026-07-07.xlsx
@@ -10,9 +10,7 @@
     <sheet name="Info" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Historial" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Historial'!$A$1:$H$12</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -20,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,13 +26,22 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000B1F3A"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -49,8 +56,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -125,6 +135,23 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaHistorialCompras" displayName="TablaHistorialCompras" ref="A1:H12" headerRowCount="1">
+  <autoFilter ref="A1:H12"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="Producto"/>
+    <tableColumn id="2" name="Lote"/>
+    <tableColumn id="3" name="Fecha compra"/>
+    <tableColumn id="4" name="Expiración"/>
+    <tableColumn id="5" name="Cantidad"/>
+    <tableColumn id="6" name="Restante"/>
+    <tableColumn id="7" name="Precio total"/>
+    <tableColumn id="8" name="Proveedor"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -418,14 +445,18 @@
   </sheetPr>
   <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="41" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
@@ -451,7 +482,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>07/07/2026 17:50</t>
+          <t>07/07/2026 17:55</t>
         </is>
       </c>
     </row>
@@ -463,7 +494,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hasta 07/07/2026 — orden: fecha de compra (reciente primero)</t>
+          <t>Hasta 07/07/2026 — orden: nombre (A→Z)</t>
         </is>
       </c>
     </row>
@@ -490,44 +521,54 @@
   </sheetPr>
   <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Producto</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Lote</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Fecha compra</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Expiración</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Cantidad</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Restante</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Precio total</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Proveedor</t>
         </is>
@@ -536,228 +577,228 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Croissant</t>
+          <t>Café molido</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>l11</t>
+          <t>l07</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10,00 €</t>
+          <t>22,00 €</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>bimbo</t>
+          <t>Cafés Origen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Fruta fresca</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>l09</t>
+          <t>l01</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1</v>
+        <v>42</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>12,00 €</t>
+          <t>18,00 €</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Frutas del Mercado</t>
+          <t>Panadería Sol</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Zumo de naranja</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>l06</t>
+          <t>l11</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>05/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>12/07/2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F4" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>15,00 €</t>
+          <t>10,00 €</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Cítricos Valle</t>
+          <t>bimbo</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Pan de molde</t>
+          <t>Fruta fresca</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>l02</t>
+          <t>l09</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>04/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
-        <v>8</v>
+        <v>2.1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4,50 €</t>
+          <t>12,00 €</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Bimbo</t>
+          <t>Frutas del Mercado</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Yogur natural</t>
+          <t>Huevos</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>l05</t>
+          <t>l10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>12,00 €</t>
+          <t>6,00 €</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Danone</t>
+          <t>Granja Local</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Croissant</t>
+          <t>Jamón serrano</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>l01</t>
+          <t>l03</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>60</v>
+        <v>2.5</v>
       </c>
       <c r="F7" t="n">
-        <v>42</v>
+        <v>1.2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>18,00 €</t>
+          <t>45,00 €</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Panadería Sol</t>
+          <t>Embutidos Norte</t>
         </is>
       </c>
     </row>
@@ -802,38 +843,38 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Huevos</t>
+          <t>Pan de molde</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>l10</t>
+          <t>l02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>6,00 €</t>
+          <t>4,50 €</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Granja Local</t>
+          <t>Bimbo</t>
         </is>
       </c>
     </row>
@@ -878,81 +919,83 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jamón serrano</t>
+          <t>Yogur natural</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>l03</t>
+          <t>l05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>27/06/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2.5</v>
+        <v>48</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2</v>
+        <v>10</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>45,00 €</t>
+          <t>12,00 €</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Embutidos Norte</t>
+          <t>Danone</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Café molido</t>
+          <t>Zumo de naranja</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>l07</t>
+          <t>l06</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>05/07/2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1</v>
+        <v>4.5</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>22,00 €</t>
+          <t>15,00 €</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Cafés Origen</t>
+          <t>Cítricos Valle</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/exports/historial_compras/historial_compras_hasta_2026-07-07.xlsx
+++ b/exports/historial_compras/historial_compras_hasta_2026-07-07.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.00&quot; €&quot;"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -29,6 +31,7 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -44,7 +47,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -52,14 +55,40 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E6EC"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E6EC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E6EC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E6EC"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -138,8 +167,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaHistorialCompras" displayName="TablaHistorialCompras" ref="A1:H12" headerRowCount="1">
-  <autoFilter ref="A1:H12"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaHistorialCompras" displayName="TablaHistorialCompras" ref="A1:H14" headerRowCount="1">
+  <autoFilter ref="A1:H14"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Producto"/>
     <tableColumn id="2" name="Lote"/>
@@ -446,11 +475,11 @@
   <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Campo</t>
@@ -462,50 +491,50 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Informe</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Historial de compras</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Generado</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>07/07/2026 17:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>07/07/2026 19:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Criterio</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Hasta 07/07/2026 — orden: nombre (A→Z)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Hasta 07/07/2026 — orden: fecha de compra (reciente primero)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Registros</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>11</v>
+      <c r="B5" s="3" t="n">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -519,476 +548,552 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Producto</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Lote</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Fecha compra</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>Expiración</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>Cantidad</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>Restante</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>Precio total</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>Proveedor</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Croissant</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>l11</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>10,00 €</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>bimbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Fruta fresca</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>l09</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>11/07/2026</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>12,00 €</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Frutas del Mercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Zumo de naranja</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>l06</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>05/07/2026</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>15,00 €</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Cítricos Valle</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Pan de molde</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>l02</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>04/07/2026</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>4,50 €</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Bimbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Yogur natural</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>l05</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>12,00 €</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Danone</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Croissant</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>l01</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>18,00 €</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Panadería Sol</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Mantequilla</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>l08</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>8,50 €</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Lácteos Sur</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Huevos</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>l10</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>6,00 €</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Granja Local</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Queso manchego</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>l04</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>28,00 €</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Quesería Manchega</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Jamón serrano</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>l03</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>27/06/2026</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>45,00 €</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Embutidos Norte</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>Café molido</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>l07</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>05/09/2026</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E12" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F12" s="5" t="n">
         <v>0.1</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>22,00 €</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>Cafés Origen</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Croissant</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>l01</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>02/07/2026</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>10/07/2026</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>60</v>
-      </c>
-      <c r="F3" t="n">
-        <v>42</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>18,00 €</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Panadería Sol</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Croissant</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>l11</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>07/07/2026</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Pan de molde</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>l13</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>5</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>10,00 €</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>bimbo</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Fruta fresca</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>l09</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>11/07/2026</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>12,00 €</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Frutas del Mercado</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Huevos</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>l10</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>30/06/2026</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>60</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>6,00 €</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Granja Local</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Jamón serrano</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>l03</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>27/06/2026</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>21/07/2026</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>45,00 €</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Embutidos Norte</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Mantequilla</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>l08</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>27/07/2026</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>8,50 €</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Lácteos Sur</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Pan de molde</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>l02</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>04/07/2026</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>14/07/2026</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>12</v>
-      </c>
-      <c r="F9" t="n">
-        <v>8</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>4,50 €</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Bimbo</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Queso manchego</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>l04</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>17/07/2026</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>28,00 €</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Quesería Manchega</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Yogur natural</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>l05</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>09/07/2026</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>48</v>
-      </c>
-      <c r="F11" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>12,00 €</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Danone</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Zumo de naranja</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>l06</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>05/07/2026</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>12/07/2026</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>10</v>
-      </c>
-      <c r="F12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>15,00 €</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Cítricos Valle</t>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>l12</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>5,00 €</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>bimbo</t>
         </is>
       </c>
     </row>
